--- a/data/trans_bre/IQ2606_R2-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IQ2606_R2-Clase-trans_bre.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5,2</t>
+          <t>3,29</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>4,11%</t>
         </is>
       </c>
     </row>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 20,82</t>
+          <t>-3,99; 20,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,72; 10,42</t>
+          <t>-9,3; 9,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,65; 21,51</t>
+          <t>-11,56; 19,59</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 44,76</t>
+          <t>-6,39; 46,77</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-9,13; 12,93</t>
+          <t>-10,13; 11,89</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-13,87; 31,72</t>
+          <t>-13,28; 28,37</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-11,42</t>
+          <t>-10,88</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-12,19%</t>
+          <t>-11,63%</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-13,31; 9,47</t>
+          <t>-11,54; 9,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,38; 11,93</t>
+          <t>-8,06; 11,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-25,53; 3,74</t>
+          <t>-25,66; 5,66</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-17,71; 15,09</t>
+          <t>-15,62; 15,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-9,05; 16,9</t>
+          <t>-10,08; 15,95</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-26,56; 3,44</t>
+          <t>-26,94; 5,96</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-18,98</t>
+          <t>-19,06</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-20,39%</t>
+          <t>-20,69%</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,84; 12,65</t>
+          <t>-11,73; 13,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-22,2; 3,08</t>
+          <t>-22,94; 3,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-50,73; 0,85</t>
+          <t>-45,77; 0,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-18,61; 23,09</t>
+          <t>-17,31; 24,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-29,13; 4,57</t>
+          <t>-29,24; 5,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-54,35; 0,15</t>
+          <t>-48,46; -0,0</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-5,39</t>
+          <t>-6,36</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-5,78%</t>
+          <t>-6,79%</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 15,46</t>
+          <t>-0,13; 15,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 10,25</t>
+          <t>-5,5; 9,12</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-18,22; 4,72</t>
+          <t>-18,37; 3,55</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 30,84</t>
+          <t>-0,15; 31,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-6,86; 15,46</t>
+          <t>-7,56; 13,75</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-18,8; 5,31</t>
+          <t>-19,39; 3,83</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7,31</t>
+          <t>5,29</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>6,64%</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 14,99</t>
+          <t>-5,33; 14,54</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-13,67; 4,4</t>
+          <t>-13,13; 5,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,53; 21,23</t>
+          <t>-12,54; 20,33</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,04; 32,55</t>
+          <t>-9,12; 32,2</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-18,55; 6,56</t>
+          <t>-17,86; 8,44</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,55; 30,52</t>
+          <t>-14,06; 28,91</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-10,55</t>
+          <t>-11,17</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-12,08%</t>
+          <t>-12,89%</t>
         </is>
       </c>
     </row>
@@ -1034,32 +1034,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-9,48; 19,85</t>
+          <t>-10,09; 21,28</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-8,03; 19,47</t>
+          <t>-8,25; 17,44</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-40,07; 10,08</t>
+          <t>-45,3; 9,35</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-16,64; 41,81</t>
+          <t>-17,27; 46,03</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-10,18; 32,58</t>
+          <t>-10,98; 28,21</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-43,19; 11,93</t>
+          <t>-49,46; 11,14</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-2,95</t>
+          <t>-3,87</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-3,4%</t>
+          <t>-4,46%</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,75; 9,62</t>
+          <t>0,42; 9,22</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 3,45</t>
+          <t>-4,03; 3,65</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-9,92; 3,66</t>
+          <t>-10,33; 3,59</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,22; 17,74</t>
+          <t>0,69; 16,76</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,8; 4,89</t>
+          <t>-5,32; 5,2</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-11,22; 4,45</t>
+          <t>-11,63; 4,17</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IQ2606_R2-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IQ2606_R2-Clase-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -520,7 +529,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si el verano pasado emplearon crema solar con factor de protección de 50 o más, siempre o casi siempre</t>
+          <t>Menores que el verano pasado emplearon crema solar con factor de protección de 50 o más, siempre o casi siempre</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -594,239 +603,163 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>8,74</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1,01</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3,29</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>16,71%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1,2%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>4,11%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>8.742624606199911</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>1.00848783936186</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>3.287744212008581</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>0.1671280767030498</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.01202224536734367</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.04110186293380415</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-3,99; 20,77</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-9,3; 9,28</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-11,56; 19,59</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-6,39; 46,77</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-10,13; 11,89</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-13,28; 28,37</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-3.993871568301496</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-9.30322096075365</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-11.55868514602461</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>-0.06391250200778703</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.1012576767667137</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.1328435131417139</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>20.77456268588477</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>9.284675815851775</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>19.59214366833034</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>0.4677187922670961</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.1189356682597299</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.2836873263155212</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Grupo III</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-0,7</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1,89</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-10,88</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-1,0%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>2,48%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-11,63%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-11,54; 9,88</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-8,06; 11,39</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-25,66; 5,66</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-15,62; 15,34</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-10,08; 15,95</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-26,94; 5,96</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-0.6979882979684549</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>1.885807447822263</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-10.884513715472</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-0.01004753430384666</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.02479445640300804</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.1162933359698918</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Grupo IV y V</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>0,87</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-9,2</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-19,06</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-12,61%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-20,69%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-11.54077134207106</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-8.061503019540526</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-25.65788305703493</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-0.1562270275187315</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.1007972753776484</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.2693800526064991</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-11,73; 13,66</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-22,94; 3,59</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-45,77; 0,86</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-17,31; 24,79</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-29,24; 5,17</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-48,46; -0,0</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>9.883249742234087</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>11.39401696274877</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>5.6568913139052</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>0.15341069761438</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.1595142391825252</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.05960576653057584</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Grupo VI</t>
+          <t>Grupo IV y V</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -834,239 +767,163 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>7,67</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>2,19</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-6,36</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>13,95%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3,11%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-6,79%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>0.8720592564730678</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-9.203556297134307</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-19.05745970825107</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>0.01404042522566982</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.1260629841062719</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.2068516352292243</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-0,13; 15,9</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-5,5; 9,12</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-18,37; 3,55</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-0,15; 31,27</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-7,56; 13,75</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-19,39; 3,83</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-11.72711345629176</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-22.94168697148628</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-45.77339198201951</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>-0.1730696221460126</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.2923531658509072</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.4846056976855939</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Grupo VII</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>13.65866196178436</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>3.586583983697672</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.856190006919186</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>0.2479380971796809</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.05172526298358383</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>-4.70867118648847e-05</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>4,53</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-4,43</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>5,29</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>8,66%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-6,4%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>6,64%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-5,33; 14,54</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-13,13; 5,39</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-12,54; 20,33</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-9,12; 32,2</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-17,86; 8,44</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-14,06; 28,91</t>
-        </is>
+      <c r="C13" s="5" t="n">
+        <v>7.668582533717927</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>2.1939907282857</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-6.362500996749231</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>0.1395194999742296</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.03114647050349735</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.06786033840394352</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>No ha trabajado</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>5,47</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>5,69</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-11,17</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>10,1%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>8,26%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-12,89%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-0.1290221830986991</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-5.504244408813479</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-18.36626604454642</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-0.001492316301975258</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.07564691222833002</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.1939499742450611</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>-10,09; 21,28</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>-8,25; 17,44</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>-45,3; 9,35</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>-17,27; 46,03</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>-10,98; 28,21</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-49,46; 11,14</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>15.89994610292465</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>9.119563847189987</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>3.554774862775216</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>0.3126513277078264</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.137464295666644</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.03825588706181919</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Grupo VII</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1074,77 +931,243 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>4,97</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-0,37</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-3,87</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>8,74%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-0,51%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-4,46%</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>4.525818757030953</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-4.433355164246333</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>5.289867204991072</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>0.0866201422885287</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.06403659946165112</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.06641387080626332</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>0,42; 9,22</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-4,03; 3,65</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-10,33; 3,59</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>0,69; 16,76</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-5,32; 5,2</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-11,63; 4,17</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-5.330558955532898</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-13.12909417964427</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-12.5367820214695</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>-0.09123205787323002</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.1786376012677801</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.1406471650806766</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>14.53799267720653</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>5.392809671896612</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>20.32621834591723</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>0.3219633306576998</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.08442242299348274</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.2890830877234645</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>5.468531851504554</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>5.688147879093486</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>-11.17265776712962</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>0.1009586203808239</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>0.08263222878741426</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-0.1288504962128327</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>-10.09218635764481</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>-8.248124841996619</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>-45.30248605327677</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>-0.1727235713226695</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-0.109846788023928</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-0.4946498636240246</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>21.27800799604172</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>17.43784252238749</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>9.353971422264786</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>0.4603267900637562</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0.2820637069403674</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>0.1113865446967851</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>4.968760777202985</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-0.3727443924556484</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-3.865486991979794</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>0.08743235291816971</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>-0.005101478124071372</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>-0.04458618250682708</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>0.4219136736344215</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-4.032053963616121</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-10.32935321171008</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>0.006937729583852847</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>-0.05320643909815913</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>-0.1163208197728177</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>9.223981865190167</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>3.654589549328296</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>3.58579627363531</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>0.1675980070051215</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>0.05202616453266596</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>0.0417353471050969</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1153,15 +1176,15 @@
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
